--- a/s02/descargables/S02_ALU_05_Matriz_Riesgo_EBR_EN_BLANCO.xlsx
+++ b/s02/descargables/S02_ALU_05_Matriz_Riesgo_EBR_EN_BLANCO.xlsx
@@ -714,7 +714,7 @@
     <t xml:space="preserve">Cap. XIV, Arts. 42 a 51</t>
   </si>
   <si>
-    <t xml:space="preserve">Programa de revisión anual y designación de quien emite el dictamen: área interna si tu riesgo es bajo o medio; auditor externo certificado por la UIF si es alto (ver A6).</t>
+    <t xml:space="preserve">Programa de revisión anual y designación de quien emite el dictamen: puede ser el área interna si tu riesgo es bajo o medio (Art. 44); auditor externo certificado por la UIF si es alto, o si así lo eliges (Art. 45). Ver A6.</t>
   </si>
   <si>
     <t xml:space="preserve">Manual, numeral 10.1</t>
@@ -792,7 +792,7 @@
     <t xml:space="preserve">Cómo se calcula: Efectividad = suma de los porcentajes ÷ obligaciones exigibles. El denominador es fijo (14) y solo baja cuando una obligación es «No aplica». Por eso registrar menos controles ya NO mejora el resultado: lo empeora.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sólo las fracciones V, VIII y X admiten «No aplica», y de forma condicionada: V para quien opera exclusivamente con Clientes ocasionales sin Relación de Negocios; VIII para las fracciones cuyo umbral no admite acumulación; X para la persona física que realiza la Actividad Vulnerable sin estructura, porque el Art. 20 de la Ley ata la designación a las personas morales. Las otras once no admiten exclusión.</t>
+    <t xml:space="preserve">El Art. 37 Bis 2 no enlista fracciones: exenta cualquier contenido del Manual referido a actos u operaciones que se determine no realizar, con constancia en el propio Manual. Que en esta matriz sólo se habilite «No aplica» en las fracciones V, VIII y X es criterio de la herramienta, y de forma condicionada: V para quien opera exclusivamente con Clientes ocasionales sin Relación de Negocios; VIII para las fracciones cuyo umbral no admite acumulación; X para la persona física que realiza la Actividad Vulnerable sin estructura, porque el Art. 20 de la Ley ata la designación a las personas morales. Las otras once no admiten exclusión.</t>
   </si>
   <si>
     <t xml:space="preserve">El Art. 48 fr. V exige que el auditor verifique que la exclusión no actualice un incumplimiento y que sea consistente con el análisis de Riesgos. Por eso la justificación pide el numeral del Manual donde consta la exención, no un texto libre.</t>
@@ -1071,7 +1071,7 @@
     <t xml:space="preserve">Evidencia</t>
   </si>
   <si>
-    <t xml:space="preserve">El compromiso debe indicar al menos el año y el mes (Art. 10 Septies 2, fr. IV). Un plan sin fecha no acredita mitigación: acredita intención.</t>
+    <t xml:space="preserve">El Art. 10 Septies 2, último párrafo, pide indicar al menos el año y mes EN QUE SE OBTUVIERON LOS RESULTADOS de la implementación: ése ancla el plazo de doce meses. La fecha comprometida de la acción es buena práctica de esta matriz. Un plan sin fecha no acredita mitigación: acredita intención.</t>
   </si>
   <si>
     <t xml:space="preserve">A9 · CONSTANCIA DE LA EVALUACIÓN, FUENTES Y CONSERVACIÓN</t>
@@ -1413,7 +1413,7 @@
     <t xml:space="preserve">No es Persona Políticamente Expuesta</t>
   </si>
   <si>
-    <t xml:space="preserve">Anexo 10 · RCG 23 Bis 3 y 23 Bis 4</t>
+    <t xml:space="preserve">Declaración del Cliente y consulta en Consulta PEP 2.0 · RCG 23 Quáter 1 · RCG 23 Bis 3 y 23 Bis 4</t>
   </si>
   <si>
     <t xml:space="preserve">PEP nacional, comportamiento congruente con ingresos y funciones</t>
@@ -1932,7 +1932,7 @@
     <t xml:space="preserve">Cambio en la condición de Persona Políticamente Expuesta</t>
   </si>
   <si>
-    <t xml:space="preserve">RCG 23 Quáter · Anexo 10</t>
+    <t xml:space="preserve">RCG 23 Quáter · 23 Quáter 1 (Consulta PEP 2.0)</t>
   </si>
   <si>
     <t xml:space="preserve">Cambio significativo en la actividad, el giro o la fuente de los ingresos</t>
@@ -8975,8 +8975,8 @@
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D47" s="53" t="str">
-        <f aca="false">IF($F$46="","Falta registrar el año y el mes en que se modificarán las políticas conforme a los resultados (Art. 10 Septies 2, último párrafo).","Compromiso registrado. Los dos plazos corren en paralelo: revisar la evaluación y modificar las políticas son obligaciones distintas.")</f>
-        <v>Falta registrar el año y el mes en que se modificarán las políticas conforme a los resultados (Art. 10 Septies 2, último párrafo).</v>
+        <f aca="false">IF($F$46="","Falta registrar el año y el mes. Ojo: el Art. 10 Septies 2, último párrafo, pide el año y mes EN QUE SE OBTUVIERON LOS RESULTADOS de la implementación, que es el que ancla el plazo de doce meses.","Compromiso registrado. Los dos plazos corren en paralelo: revisar la evaluación y modificar las políticas son obligaciones distintas.")</f>
+        <v>Falta registrar el año y el mes. Ojo: el Art. 10 Septies 2, último párrafo, pide el año y mes EN QUE SE OBTUVIERON LOS RESULTADOS de la implementación, que es el que ancla el plazo de doce meses.</v>
       </c>
       <c r="E47" s="53"/>
       <c r="F47" s="53"/>
